--- a/Server/NewServer/bin/commonconfig/setting/role_relation.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/role_relation.xlsx
@@ -32,7 +32,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -43,7 +43,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认阵营 与其他阵营均友好</t>
+Default faction: friendly to all other factions</t>
         </r>
       </text>
     </comment>
@@ -58,7 +58,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-蓝队阵营</t>
+Blue team faction</t>
         </r>
       </text>
     </comment>
@@ -84,7 +84,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-红队阵营</t>
+Red team faction</t>
         </r>
       </text>
     </comment>
@@ -110,7 +110,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-黄队阵营</t>
+Yellow team faction</t>
         </r>
       </text>
     </comment>
